--- a/backend/import_A4_GROUPE_08_MAJ_complet.xlsx
+++ b/backend/import_A4_GROUPE_08_MAJ_complet.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,35 +444,45 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Bâtiment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Salle</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Date début</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Date fin</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Volume horaire (h)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Groupe</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Vague</t>
         </is>
@@ -497,31 +507,41 @@
           <t>CPFAE-AGC</t>
         </is>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>JEROME PATRICK ACHI</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DISTRICT DE LA COMOE</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>46137.33333333334</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="H2" s="1" t="n">
         <v>46138.70833333334</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>16</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>GROUPE 8</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>GROUPE 8</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -546,31 +566,41 @@
           <t>CPFAE-AGC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>JEROME PATRICK ACHI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DISTRICT DE LA COMOE</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>46139.33333333334</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="H3" s="1" t="n">
         <v>46140.70833333334</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>16</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GROUPE 8</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>GROUPE 8</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -595,31 +625,41 @@
           <t>CPFAE-AGC</t>
         </is>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ROBERT BEUGRE MAMBE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DISTRICT DU ZANZAN</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>46146.33333333334</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="H4" s="1" t="n">
         <v>46149.70833333334</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>30</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>GROUPE 8</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>GROUPE 8</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -644,31 +684,41 @@
           <t>CPFAE-AGC</t>
         </is>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ROBERT BEUGRE MAMBE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DISTRICT DU ZANZAN</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>46150.33333333334</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>46151.70833333334</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>16</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>GROUPE 8</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>GROUPE 8</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -693,31 +743,41 @@
           <t>CPFAE-AGC</t>
         </is>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ROBERT BEUGRE MAMBE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DISTRICT DU ZANZAN</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>46153.33333333334</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>46157.70833333334</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>30</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>GROUPE 8</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>GROUPE 8</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -742,31 +802,41 @@
           <t>CPFAE-AGC</t>
         </is>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ROBERT BEUGRE MAMBE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DISTRICT DU ZANZAN</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>46158.33333333334</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>46162.70833333334</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>30</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>GROUPE 8</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>GROUPE 8</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -791,31 +861,41 @@
           <t>CPFAE-AGC</t>
         </is>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ROBERT BEUGRE MAMBE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DISTRICT DU ZANZAN</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>46163.33333333334</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="H8" s="1" t="n">
         <v>46165.70833333334</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>20</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>GROUPE 8</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>GROUPE 8</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -840,31 +920,41 @@
           <t>CPFAE-AGC</t>
         </is>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ROBERT BEUGRE MAMBE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DISTRICT DU ZANZAN</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>46168.33333333334</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="H9" s="1" t="n">
         <v>46170.70833333334</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>16</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>GROUPE 8</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>GROUPE 8</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -889,31 +979,41 @@
           <t>CPFAE-AGC</t>
         </is>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ROBERT BEUGRE MAMBE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DISTRICT DU ZANZAN</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>46171.33333333334</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>46175.70833333334</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>30</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>GROUPE 8</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>GROUPE 8</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -938,31 +1038,41 @@
           <t>CPFAE-AGC</t>
         </is>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ROBERT BEUGRE MAMBE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DISTRICT DU ZANZAN</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>46177.33333333334</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="H11" s="1" t="n">
         <v>46180.70833333334</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>30</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>GROUPE 8</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>GROUPE 8</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
